--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260629.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>885,744,000</t>
+          <t>887,744,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.35%</t>
+          <t>10.32%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.16%</t>
+          <t>10.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.60%</t>
+          <t>6.29%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>5.00%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>37,885,000</t>
+          <t>38,465,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.47%</t>
         </is>
       </c>
     </row>
@@ -726,73 +726,73 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,979,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>93,988,442</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>4,979,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -880,73 +880,73 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>1,772</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1,772</t>
+          <t>30,516,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>144,992,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>130,197,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>97,767,000</t>
+          <t>98,167,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>360,175,000</t>
+          <t>364,675,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>79,488,000</t>
+          <t>79,888,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>270,866,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>14,293,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,243,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,672,010,141</t>
+          <t>4,274,033,547</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,230,650,103</t>
+          <t>10,621,907,703</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-202,261,844</t>
+          <t>-135,186,363</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
